--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MCA\CAP776_Python\Demo\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E51CF8-51CA-4FEF-B9B1-40C5F1CCDC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED60741-A900-4EAD-BC5D-7654773A2B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t xml:space="preserve">Average </t>
+  </si>
+  <si>
+    <t>Working</t>
   </si>
 </sst>
 </file>
@@ -1124,26 +1127,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>300</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MCA\CAP776_Python\Demo\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED60741-A900-4EAD-BC5D-7654773A2B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D62DB8B-2A4F-4379-B509-80CDCA8CA668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1173,26 +1173,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B10" s="14">
+        <v>300</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>450</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MCA\CAP776_Python\Demo\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D62DB8B-2A4F-4379-B509-80CDCA8CA668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0577A6-658C-4675-BFAE-4F1BC3D50E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>Working</t>
+  </si>
+  <si>
+    <t>working</t>
+  </si>
+  <si>
+    <t>preparing for CA</t>
   </si>
 </sst>
 </file>
@@ -1219,70 +1225,142 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B11" s="14">
+        <v>350</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>400</v>
+      </c>
+      <c r="G11" s="14">
+        <v>8</v>
+      </c>
+      <c r="H11" s="14">
+        <v>450</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>150</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12" s="14">
+        <v>540</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B13" s="14">
+        <v>300</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
